--- a/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,7 +451,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>3</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>653</v>
+        <v>729</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>25</v>
@@ -753,7 +753,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>

--- a/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,11 +451,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1053,27 +1053,25 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>令和7年4月1日</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6578000</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>富士フイルムメディカル株式会社北関東支社さいたま市大宮区浅間町2-240</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>一般撮影（レントゲン）</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>保守</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>6,578,000</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1100,27 +1098,25 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>令和7年4月1日</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>日成メディカル宇都宮市問屋町3426-39</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>血管撮影（CVS、アンギオ）</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>保守</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>16,500,000</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1147,27 +1143,25 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t>令和6年5月26日</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3685000</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
           <t>キヤノンメディカルシステムズ栃木県大田原市下石上1385番地</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>一般撮影（レントゲン）</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>製品</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3,685,000</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">

--- a/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -512,7 +512,7 @@
         <v>165</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
@@ -536,7 +536,7 @@
         <v>159</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
@@ -664,13 +664,9 @@
         <v>62</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>X線関連契約の該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>さいたま赤十字病院_随意契約_X線関連.xlsx</t>
@@ -735,7 +731,7 @@
         <v>729</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -818,40 +814,40 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>小川赤十字病院</t>
+          <t>さいたま赤十字病院</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>アンギオ装置保守</t>
+          <t>移動型デジタル式汎用X線透視診断装置</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>平成２８年 １ 月 １ 日</t>
+          <t>令和7年5月30日</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4995000</v>
+        <v>19250000</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>株式会社 シーメンスジャパンさいたま市北区宮原町２－１０３－３０</t>
+          <t>株式会社 栗原医療機器店 さいたま支店 さいたま市見沼区東大宮6-3-1</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ogawa.jrc.or.jp/bid/zuikei27.pdf</t>
+          <t>https://www.saitama-med.jrc.or.jp/albums/abm00003351.pdf</t>
         </is>
       </c>
     </row>
@@ -863,21 +859,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>深谷赤十字病院</t>
+          <t>小川赤十字病院</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>血管造影装置Innoova IGS360保守</t>
+          <t>アンギオ装置保守</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>令和8年1月20日</t>
+          <t>平成２８年 １ 月 １ 日</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>10492020</v>
+        <v>4995000</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -891,12 +887,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>GEヘルスケア・ジャパン株式会社埼玉県さいたま市北区宮原町1-853-8ウエルネスキューブ大宮</t>
+          <t>株式会社 シーメンスジャパンさいたま市北区宮原町２－１０３－３０</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukaya.jrc.or.jp/announcement/?fileid=00000090</t>
+          <t>https://www.ogawa.jrc.or.jp/bid/zuikei27.pdf</t>
         </is>
       </c>
     </row>
@@ -913,7 +909,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>乳房用デジタルX線撮影装置Senographe Pristina保守</t>
+          <t>血管造影装置Innoova IGS360保守</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -922,11 +918,11 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3039960</v>
+        <v>10492020</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -958,16 +954,16 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FPDシステムなどの保守契約</t>
+          <t>乳房用デジタルX線撮影装置Senographe Pristina保守</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>令和8年3月23日</t>
+          <t>令和8年1月20日</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>9442488</v>
+        <v>3039960</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -981,7 +977,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>富士フィルムメディカル㈱埼玉県さいたま市大宮区浅間町2-240</t>
+          <t>GEヘルスケア・ジャパン株式会社埼玉県さいたま市北区宮原町1-853-8ウエルネスキューブ大宮</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1003,16 +999,16 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>一般撮影装置（RADspeed Pro DRpack) 3式 保守点検契約</t>
+          <t>FPDシステムなどの保守契約</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>令和7年12月26日</t>
+          <t>令和8年3月23日</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>13015320</v>
+        <v>9442488</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1026,38 +1022,38 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>島津メディカルシステム(株)東京支社埼玉営業所埼玉県さいたま市南区内谷5-3-2</t>
+          <t>富士フィルムメディカル㈱埼玉県さいたま市大宮区浅間町2-240</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fukaya.jrc.or.jp/announcement/?fileid=00000085</t>
+          <t>https://www.fukaya.jrc.or.jp/announcement/?fileid=00000090</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>栃木県</t>
+          <t>埼玉県</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>芳賀赤十字病院</t>
+          <t>深谷赤十字病院</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムＦＰＤ（フラットパネルディスプレイ）装置及びＸ線回診車（フラットパネル含む）の保守契約（更新）</t>
+          <t>一般撮影装置（RADspeed Pro DRpack) 3式 保守点検契約</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月1日</t>
+          <t>令和7年12月26日</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>6578000</v>
+        <v>13015320</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1071,12 +1067,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社北関東支社さいたま市大宮区浅間町2-240</t>
+          <t>島津メディカルシステム(株)東京支社埼玉営業所埼玉県さいたま市南区内谷5-3-2</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://www.haga.jrc.or.jp/data/media/haga/page/about/procurement/Reiwa7.pdf</t>
+          <t>https://www.fukaya.jrc.or.jp/announcement/?fileid=00000085</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>血管造影撮影装置保守</t>
+          <t>富士フイルムＦＰＤ（フラットパネルディスプレイ）装置及びＸ線回診車（フラットパネル含む）の保守契約（更新）</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1102,11 +1098,11 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>16500000</v>
+        <v>6578000</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1116,7 +1112,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>日成メディカル宇都宮市問屋町3426-39</t>
+          <t>富士フイルムメディカル株式会社北関東支社さいたま市大宮区浅間町2-240</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1138,35 +1134,35 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>一般撮影装置X線電圧発生器</t>
+          <t>血管造影撮影装置保守</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>令和6年5月26日</t>
+          <t>令和7年4月1日</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3685000</v>
+        <v>16500000</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>キヤノンメディカルシステムズ栃木県大田原市下石上1385番地</t>
+          <t>日成メディカル宇都宮市問屋町3426-39</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://www.haga.jrc.or.jp/data/media/haga/page/about/procurement/令和６年度随意契約の公表について.pdf</t>
+          <t>https://www.haga.jrc.or.jp/data/media/haga/page/about/procurement/Reiwa7.pdf</t>
         </is>
       </c>
     </row>
@@ -1178,21 +1174,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>足利赤十字病院</t>
+          <t>芳賀赤十字病院</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>デジタル式乳房用X線撮影装置保守</t>
+          <t>一般撮影装置X線電圧発生器</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2023年9月1日</t>
+          <t>令和6年5月26日</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1384920</v>
+        <v>3685000</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1201,17 +1197,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>富士フィルムメディカル株式会社さいたま市大宮区浅間町2-240</t>
+          <t>キヤノンメディカルシステムズ栃木県大田原市下石上1385番地</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://www.ashikaga.jrc.or.jp/files/libs/4469/202310260953243744.pdf</t>
+          <t>https://www.haga.jrc.or.jp/data/media/haga/page/about/procurement/令和６年度随意契約の公表について.pdf</t>
         </is>
       </c>
     </row>
@@ -1228,20 +1224,20 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>シーメンス社製装置（ガンマカメラ・アンギオ・MRI）の変更保守契約</t>
+          <t>デジタル式乳房用X線撮影装置保守</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2025年1月1日</t>
+          <t>2023年9月1日</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>99646108</v>
+        <v>1384920</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1251,12 +1247,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>シーメンスヘルスケア株式会社北関東営業所埼玉県さいたま市大宮区土手町1-49-8</t>
+          <t>富士フィルムメディカル株式会社さいたま市大宮区浅間町2-240</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://www.ashikaga.jrc.or.jp/files/libs/7091/202506021147286443.pdf</t>
+          <t>https://www.ashikaga.jrc.or.jp/files/libs/4469/202310260953243744.pdf</t>
         </is>
       </c>
     </row>
@@ -1273,16 +1269,16 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>X 線血管造影診断装置保守契約</t>
+          <t>シーメンス社製装置（ガンマカメラ・アンギオ・MRI）の変更保守契約</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2025年10月1日</t>
+          <t>2025年1月1日</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>52668000</v>
+        <v>99646108</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1301,7 +1297,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://www.ashikaga.jrc.or.jp/files/libs/7092/202601271005459505.pdf</t>
+          <t>https://www.ashikaga.jrc.or.jp/files/libs/7091/202506021147286443.pdf</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1314,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FPD装置保守契約</t>
+          <t>X 線血管造影診断装置保守契約</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1327,11 +1323,11 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>7154400</v>
+        <v>52668000</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1341,7 +1337,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>富士フィルムメディカル株式会社北関東支社埼玉県さいたま市大宮区浅間町2-240</t>
+          <t>シーメンスヘルスケア株式会社北関東営業所埼玉県さいたま市大宮区土手町1-49-8</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1358,21 +1354,21 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>那須赤十字病院</t>
+          <t>足利赤十字病院</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>デジタルラジオグラフィー二式</t>
+          <t>FPD装置保守契約</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>令和7年8月2日</t>
+          <t>2025年10月1日</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7700000</v>
+        <v>7154400</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1381,17 +1377,17 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
+          <t>富士フィルムメディカル株式会社北関東支社埼玉県さいたま市大宮区浅間町2-240</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
+          <t>https://www.ashikaga.jrc.or.jp/files/libs/7092/202601271005459505.pdf</t>
         </is>
       </c>
     </row>
@@ -1408,30 +1404,30 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>長尺リーダー撮影台</t>
+          <t>X線循環器診断システムINFX-8000/HE保守契約の更新について</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>令和8年3月2日</t>
+          <t>令和7年7月14日</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3300000</v>
+        <v>9372000</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
+          <t>キャノンメディカルシステムズ株式会社栃木県宇都宮市大通り1-4-24ＭＳＣビル</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1453,35 +1449,35 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>多目的デジタルX線TVシステム及び超音波診断装置各種の保守</t>
+          <t>デジタルラジオグラフィー二式</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和7年8月2日</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3205796</v>
+        <v>7700000</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
+          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
         </is>
       </c>
     </row>
@@ -1498,20 +1494,20 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>X線一般撮影装置 MRAD-A80S/5Gの修理</t>
+          <t>移動型デジタル式汎用一体型X線透視診断装置の定期点検契約の締結について</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月24日</t>
+          <t>令和7年11月6日</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2310000</v>
+        <v>2100000</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1521,12 +1517,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
+          <t>シーメンスヘルスケア株式会社埼玉県さいたま市大宮区土手町1-49-8ＧＭ大宮ビル2階</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
         </is>
       </c>
     </row>
@@ -1543,97 +1539,97 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>デジタルラジオグラフィー</t>
+          <t>X線循環器診断システムINFX-8000/T7保守契約の更新について</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>令和7年3月3日</t>
+          <t>令和7年12月3日</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>4840000</v>
+        <v>5709000</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
+          <t>キャノンメディカルシステムズ株式会社栃木県宇都宮市大通り1-4-24ＭＳＣビル</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>デジタルX線ＴＶシステムAstorex i9の保守</t>
+          <t>長尺リーダー撮影台</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和8年3月2日</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3544200</v>
+        <v>3300000</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
+          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>一般X線撮影装置の保守</t>
+          <t>多目的デジタルX線TVシステム及び超音波診断装置各種の保守</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1642,11 +1638,11 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1899480</v>
+        <v>3205796</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1656,38 +1652,38 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+          <t>X線一般撮影装置 MRAD-A80S/5Gの修理</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和6年4月24日</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1768140</v>
+        <v>2310000</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1701,42 +1697,42 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>デジタル式乳房X線撮影装置 Dimension保守</t>
+          <t>X線循環器診断システム INFX-8000V/T7保守</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>令和5年4月1日</t>
+          <t>令和6年12月16日</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4455000</v>
+        <v>5709000</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1746,38 +1742,38 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>株式会社メディス長岡市旭岡1-19</t>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+          <t>デジタルラジオグラフィー</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>令和5年4月1日</t>
+          <t>令和7年3月3日</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2665740</v>
+        <v>4840000</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1786,47 +1782,47 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>保守</t>
+          <t>製品</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>新潟県</t>
+          <t>栃木県</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>長岡赤十字病院</t>
+          <t>那須赤十字病院</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>小児救急撮影室X線撮影装置の管球交換修理</t>
+          <t>X線循環器診断システム INFX-8000V/T7保守</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>令和5年4月21日</t>
+          <t>令和5年12月16日</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3942400</v>
+        <v>5709000</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1836,12 +1832,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>丸文通商株式会社石川県金沢市松島1丁目40</t>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/cedc5f5de7ee0a81ac11fca4330a2212.pdf</t>
         </is>
       </c>
     </row>
@@ -1858,20 +1854,20 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>バイプレーン心臓血管撮影装置 Artis zee BC 保守</t>
+          <t>デジタルX線ＴＶシステムAstorex i9の保守</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月1日</t>
+          <t>令和6年4月1日</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>18367800</v>
+        <v>3544200</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1881,12 +1877,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>株式会社メディス長岡市旭岡1-19</t>
+          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
         </is>
       </c>
     </row>
@@ -1903,33 +1899,348 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>一般X線撮影装置の保守</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>令和6年4月1日</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1899480</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
           <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>令和6年4月1日</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1768140</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>デジタル式乳房X線撮影装置 Dimension保守</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>令和5年4月1日</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>4455000</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>株式会社メディス長岡市旭岡1-19</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>令和5年4月1日</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>2665740</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>小児救急撮影室X線撮影装置の管球交換修理</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>令和5年4月21日</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3942400</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>丸文通商株式会社石川県金沢市松島1丁目40</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>X線透視診断装置 CUEVISTA保守</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>令和7年4月1日</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E31" s="5" t="n">
+        <v>1201200</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>透視撮影台（X線テレビ）</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>株式会社メディス長岡市旭岡1-19</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>バイプレーン心臓血管撮影装置 Artis zee BC 保守</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>令和7年4月1日</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>18367800</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>株式会社メディス長岡市旭岡1-19</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>長岡赤十字病院</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>令和7年4月1日</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
         <v>1768140</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>保守</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
         </is>

--- a/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/新潟栃木群馬埼玉_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
